--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>764.34</v>
+        <v>755.8200000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4629.15</v>
+        <v>4645.67</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5676.23</v>
+        <v>5737.96</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3985.13</v>
+        <v>4005.71</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5325.99</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7174.29</v>
+        <v>7102.91</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7079.92</v>
+        <v>7064.59</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>294.82</v>
+        <v>293.58</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35044.2</v>
+        <v>34747.35</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>56782.52</v>
+        <v>57173.36</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>521.79</v>
+        <v>526.25</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3302.7</v>
+        <v>3330.93</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8237.030000000001</v>
+        <v>8307.42</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>90429.50999999999</v>
+        <v>91202.3</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6017.52</v>
+        <v>6068.95</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>495.54</v>
+        <v>495.2</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7462.46</v>
+        <v>7457.36</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2416.79</v>
+        <v>2415.14</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>994.85</v>
+        <v>991.4299999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10938.6</v>
+        <v>11010.29</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9070.74</v>
+        <v>9291.32</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>26924.11</v>
+        <v>27740.53</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>11574.48</v>
+        <v>11634.27</v>
       </c>
     </row>
     <row r="25">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>510.78</v>
+        <v>508.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2755-38-CM26</t>
+          <t>2755-37-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>RASTRO RETAIL SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.888.564-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2766</v>
+        <v>1363.57</v>
       </c>
     </row>
     <row r="27">
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2888.1</v>
+        <v>2896.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2755-37-CM26</t>
+          <t>2755-38-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>RASTRO RETAIL SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.888.564-6</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1359.84</v>
+        <v>2773.59</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1876.07</v>
+        <v>1862.63</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>13219.46</v>
+        <v>13124.76</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3554.35</v>
+        <v>3549.12</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8966.209999999999</v>
+        <v>9012.629999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7595.58</v>
+        <v>7931.01</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>20895.78</v>
+        <v>21240.17</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4755.2</v>
+        <v>4766.9</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6702.97</v>
+        <v>6719.46</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2835.79</v>
+        <v>2815.78</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5097.98</v>
+        <v>5190.41</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14114.27</v>
+        <v>14370.17</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>330.23</v>
+        <v>328.12</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>15684.54</v>
+        <v>15184.41</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>349.78</v>
+        <v>338.63</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4349.55</v>
+        <v>4235.01</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4652.41</v>
+        <v>4529.89</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11327.64</v>
+        <v>11467.05</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>278.17</v>
+        <v>283.43</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>667.13</v>
+        <v>673.14</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8930.110000000001</v>
+        <v>9010.549999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3192.33</v>
+        <v>3212.75</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3823.07</v>
+        <v>3847.53</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>541</v>
+        <v>538.6799999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>978.37</v>
+        <v>972.5</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>14347.8</v>
+        <v>14152.74</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1670.38</v>
+        <v>1647.67</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>24070.19</v>
+        <v>23864.89</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1286.46</v>
+        <v>1300.85</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5167.58</v>
+        <v>5116.05</v>
       </c>
     </row>
     <row r="58">
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3423.37</v>
+        <v>3408.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>316-299-CM26</t>
+          <t>2427-433-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12725.66</v>
+        <v>6213.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4105-346-CM26</t>
+          <t>316-299-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4820.12</v>
+        <v>12587.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2427-433-CM26</t>
+          <t>4105-346-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6282.23</v>
+        <v>4767.68</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11053.99</v>
+        <v>11166.4</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>769402.91</v>
+        <v>763566.01</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8875.76</v>
+        <v>8725.790000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2107.63</v>
+        <v>2117.2</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6029.27</v>
+        <v>6056.65</v>
       </c>
     </row>
     <row r="67">
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3228.87</v>
+        <v>3276.94</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>898-2056-CM26</t>
+          <t>4968-867-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4607,13 +4607,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>265.22</v>
+        <v>1307.11</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4968-867-CM26</t>
+          <t>898-2056-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1278.28</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="70">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3228.87</v>
+        <v>3251.16</v>
       </c>
     </row>
     <row r="71">
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3172.91</v>
+        <v>3194.81</v>
       </c>
     </row>
     <row r="72">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>8487.040000000001</v>
+        <v>8572.4</v>
       </c>
     </row>
     <row r="73">
@@ -4916,13 +4916,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10443.05</v>
+        <v>10511.13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2755-280-CM26</t>
+          <t>3776-370-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4977,13 +4977,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1054.47</v>
+        <v>5095.46</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4548-435-CM26</t>
+          <t>3776-369-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5003,17 +5003,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5038,13 +5038,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3856.33</v>
+        <v>4099.74</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2424-917-CM26</t>
+          <t>3882-277-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5064,17 +5064,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>10009.36</v>
+        <v>1426.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3882-277-CM26</t>
+          <t>2424-917-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5125,17 +5125,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5160,13 +5160,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1423.64</v>
+        <v>10032.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3776-369-CM26</t>
+          <t>2755-280-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5221,13 +5221,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4090.36</v>
+        <v>1056.89</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3776-370-CM26</t>
+          <t>4548-435-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5083.8</v>
+        <v>3865.17</v>
       </c>
     </row>
     <row r="80">
@@ -5343,13 +5343,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>6891.47</v>
+        <v>6937.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2424-927-CM26</t>
+          <t>4968-1056-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5404,13 +5404,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>19628.09</v>
+        <v>1092.62</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2755-285-CM26</t>
+          <t>2428-765-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5430,17 +5430,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1736.46</v>
+        <v>3314.2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2428-765-CM26</t>
+          <t>2211-673-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5491,17 +5491,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5526,13 +5526,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3292.16</v>
+        <v>2368.47</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4968-1056-CM26</t>
+          <t>2424-927-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1085.35</v>
+        <v>19759.47</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2211-673-CM26</t>
+          <t>2755-285-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5618,12 +5618,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5648,13 +5648,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2352.72</v>
+        <v>1748.08</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1431841-784-CM26</t>
+          <t>1431841-785-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5709,13 +5709,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5341.12</v>
+        <v>390.81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1431841-785-CM26</t>
+          <t>1431841-784-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5770,13 +5770,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>388.22</v>
+        <v>5376.88</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3515-328-CM26</t>
+          <t>1431841-789-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5796,17 +5796,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5831,13 +5831,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3429.03</v>
+        <v>1794.53</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2755-286-CM26</t>
+          <t>4301-480-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5892,13 +5892,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>17106.64</v>
+        <v>2923.96</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2424-938-CM26</t>
+          <t>2698-178-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5918,17 +5918,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5953,13 +5953,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8990.48</v>
+        <v>7062.75</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4548-437-CM26</t>
+          <t>3882-283-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5979,17 +5979,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>9398.76</v>
+        <v>37791.67</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3882-283-CM26</t>
+          <t>3515-328-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6040,17 +6040,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6075,13 +6075,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>37529.03</v>
+        <v>3453.03</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4301-480-CM26</t>
+          <t>2424-938-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6101,17 +6101,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2903.64</v>
+        <v>9053.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2698-178-CM26</t>
+          <t>2755-286-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6197,13 +6197,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7013.67</v>
+        <v>17226.36</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1431841-789-CM26</t>
+          <t>4548-437-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6223,17 +6223,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1782.05</v>
+        <v>9464.540000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2155.06</v>
+        <v>2170.14</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2737-451-CM26</t>
+          <t>3515-329-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6345,17 +6345,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6380,13 +6380,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>16617.08</v>
+        <v>3581.02</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3515-329-CM26</t>
+          <t>2737-451-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6406,17 +6406,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3592.37</v>
+        <v>16564.59</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3776-376-CM26</t>
+          <t>4301-489-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6467,17 +6467,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6135.54</v>
+        <v>1649.2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4105-481-CM26</t>
+          <t>1134432-525-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6563,13 +6563,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4647.54</v>
+        <v>650.48</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3776-377-CM26</t>
+          <t>2698-179-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6589,17 +6589,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6624,13 +6624,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>25838.28</v>
+        <v>1115.07</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1134432-525-CM26</t>
+          <t>4105-481-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6685,13 +6685,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>651.9</v>
+        <v>4637.43</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2698-179-CM26</t>
+          <t>3776-376-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1117.5</v>
+        <v>6122.19</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4301-489-CM26</t>
+          <t>3776-377-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6772,17 +6772,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1652.8</v>
+        <v>25782.06</v>
       </c>
     </row>
     <row r="105">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10925.09</v>
+        <v>10903.19</v>
       </c>
     </row>
     <row r="106">
@@ -6929,7 +6929,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3442.36</v>
+        <v>3435.45</v>
       </c>
     </row>
     <row r="107">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7578.67</v>
+        <v>7534.8</v>
       </c>
     </row>
     <row r="108">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>22716.06</v>
+        <v>22349.47</v>
       </c>
     </row>
     <row r="109">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10480.9</v>
+        <v>10311.77</v>
       </c>
     </row>
     <row r="110">
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>16310.3</v>
+        <v>16120.52</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2424-1001-CM26</t>
+          <t>2799-739-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7219,12 +7219,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7234,13 +7234,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>20451.79</v>
+        <v>816.71</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2799-739-CM26</t>
+          <t>2424-1001-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>821.27</v>
+        <v>20338.4</v>
       </c>
     </row>
     <row r="113">
@@ -7356,7 +7356,190 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>590.24</v>
+        <v>594.1900000000001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>3596-606-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>69.050.300-K</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>2636.97</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1285502-21-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>69.061.400-6</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>76.000.258-5</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>5239.55</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>3381-193-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>75.245.100-1</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>2113.63</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>574-428-CM25</t>
+          <t>3047-45-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.606.610-2</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>INVERSIONES SANTA FRANCISCA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.721.515-9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>755.8200000000001</v>
+        <v>1415.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4105-781-CM25</t>
+          <t>1704-1970-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVIVAC INTERNATIONAL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.971.640-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4645.67</v>
+        <v>5663.55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2698-274-CM25</t>
+          <t>1431841-276-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5737.96</v>
+        <v>7118.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3596-801-CM25</t>
+          <t>898-3946-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>KUB CHILE SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.820.166-6</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4005.71</v>
+        <v>607.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3333-431-CM25</t>
+          <t>574-428-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.061.200-3</t>
+          <t>61.606.610-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLMUE</t>
+          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AGROINDUSTRIAS DEL SUR SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.359.833-0</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5273</v>
+        <v>755.8200000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2698-307-CM25</t>
+          <t>4105-781-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7102.91</v>
+        <v>4645.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2428-1996-CM25</t>
+          <t>2698-274-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7064.59</v>
+        <v>5737.96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1823-262-CM25</t>
+          <t>3596-801-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.008.000-6</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+          <t>KUB CHILE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.616.370-6</t>
+          <t>77.820.166-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>293.58</v>
+        <v>4005.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1943-735-CM25</t>
+          <t>3333-431-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>AGROINDUSTRIAS DEL SUR SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.359.833-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>34747.35</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3776-760-CM25</t>
+          <t>2698-307-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>57173.36</v>
+        <v>7102.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4301-4125-CM25</t>
+          <t>2428-1996-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>526.25</v>
+        <v>7064.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>316-963-CM25</t>
+          <t>1823-262-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>Servicio Nacional de Menores</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA SIBESA SPA</t>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.126.547-4</t>
+          <t>78.616.370-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3330.93</v>
+        <v>293.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4301-4124-CM25</t>
+          <t>1943-735-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8307.42</v>
+        <v>34747.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1431841-564-CM25</t>
+          <t>3776-760-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1355,24 +1355,20 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>91202.3</v>
+        <v>57173.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1704-7066-CM25</t>
+          <t>4301-4125-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6068.95</v>
+        <v>526.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4968-60-CM26</t>
+          <t>4301-4124-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>495.2</v>
+        <v>8307.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3086-14-CM26</t>
+          <t>316-963-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.102.005-8</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7457.36</v>
+        <v>3330.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3086-15-CM26</t>
+          <t>1704-7066-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.102.005-8</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2415.14</v>
+        <v>6068.95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2945-17-CM26</t>
+          <t>1431841-564-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.102.004-K</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,28 +1652,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>991.4299999999999</v>
+        <v>91202.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4964-5-CM26</t>
+          <t>4968-60-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11010.29</v>
+        <v>495.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3776-34-CM26</t>
+          <t>3086-14-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.102.005-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>CENTRO DE ABASTECIMIENTO (V)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9291.32</v>
+        <v>7457.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2594-113-CM26</t>
+          <t>3086-15-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>61.102.005-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>CENTRO DE ABASTECIMIENTO (V)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>27740.53</v>
+        <v>2415.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3333-66-CM26</t>
+          <t>2945-17-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.061.200-3</t>
+          <t>61.102.004-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLMUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AGROINDUSTRIAS DEL SUR SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.359.833-0</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>11634.27</v>
+        <v>991.4299999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1048-51-CM26</t>
+          <t>4964-5-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.292.846-7</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>508.62</v>
+        <v>11010.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2755-37-CM26</t>
+          <t>3776-34-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,27 +1992,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>RASTRO RETAIL SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.888.564-6</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1363.57</v>
+        <v>9291.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1134432-116-CM26</t>
+          <t>2594-113-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2896.03</v>
+        <v>27740.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2755-38-CM26</t>
+          <t>3333-66-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>AGROINDUSTRIAS DEL SUR SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>76.359.833-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2773.59</v>
+        <v>11634.27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2698-29-CM26</t>
+          <t>1048-51-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,22 +2180,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA SIBESA SPA</t>
+          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.126.547-4</t>
+          <t>77.292.846-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1862.63</v>
+        <v>508.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2211-189-CM26</t>
+          <t>2755-38-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>13124.76</v>
+        <v>2773.59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1499899-51-CM26</t>
+          <t>2755-37-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,22 +2302,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>RASTRO RETAIL SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>77.888.564-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3549.12</v>
+        <v>1363.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2945-141-CM26</t>
+          <t>1134432-116-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,22 +2363,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.102.004-K</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9012.629999999999</v>
+        <v>2896.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3232-119-CM26</t>
+          <t>2211-189-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,27 +2419,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7931.01</v>
+        <v>13124.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>316-131-CM26</t>
+          <t>2698-29-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.000.258-5</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>21240.17</v>
+        <v>1862.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4105-152-CM26</t>
+          <t>1499899-51-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>Servicio Nacional de Reinserción Social Juvenil</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4766.9</v>
+        <v>3549.12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2783-243-CM26</t>
+          <t>2945-141-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>61.102.004-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6719.46</v>
+        <v>9012.629999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2783-253-CM26</t>
+          <t>3232-119-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2668,22 +2668,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2815.78</v>
+        <v>7931.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2428-193-CM26</t>
+          <t>316-131-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2729,22 +2729,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.000.258-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5190.41</v>
+        <v>21240.17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1943-65-CM26</t>
+          <t>4105-152-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14370.17</v>
+        <v>4766.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1285502-5-CM26</t>
+          <t>2783-243-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2851,22 +2851,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>328.12</v>
+        <v>6719.46</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3446-42-CM26</t>
+          <t>2783-253-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,27 +2907,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SERVIVAC INTERNATIONAL</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.971.640-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>15184.41</v>
+        <v>2815.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>574-131-CM26</t>
+          <t>2428-193-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.610-2</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>338.63</v>
+        <v>5190.41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1079516-310-CM26</t>
+          <t>1943-65-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4235.01</v>
+        <v>14370.17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1079516-309-CM26</t>
+          <t>1285502-5-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4529.89</v>
+        <v>328.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4964-25-CM26</t>
+          <t>574-131-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.606.610-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11467.05</v>
+        <v>338.63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2799-417-CM26</t>
+          <t>3446-42-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SERVIVAC INTERNATIONAL</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.971.640-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>283.43</v>
+        <v>15184.41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4964-27-CM26</t>
+          <t>1079516-309-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>SECCIÓN COMPRAS V ZONA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>673.14</v>
+        <v>4529.89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3776-217-CM26</t>
+          <t>1079516-310-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>SECCIÓN COMPRAS V ZONA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9010.549999999999</v>
+        <v>4235.01</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3596-299-CM26</t>
+          <t>4964-25-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3212.75</v>
+        <v>11467.05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2698-95-CM26</t>
+          <t>2799-417-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3461,22 +3461,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3847.53</v>
+        <v>283.43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1285502-10-CM26</t>
+          <t>4964-27-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>538.6799999999999</v>
+        <v>673.14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4301-271-CM26</t>
+          <t>3776-217-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>972.5</v>
+        <v>9010.549999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1704-1807-CM26</t>
+          <t>3596-299-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>14152.74</v>
+        <v>3212.75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1431841-382-CM26</t>
+          <t>2698-95-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1647.67</v>
+        <v>3847.53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2424-580-CM26</t>
+          <t>1285502-10-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>23864.89</v>
+        <v>538.6799999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4968-718-CM26</t>
+          <t>4301-271-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1300.85</v>
+        <v>972.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2428-472-CM26</t>
+          <t>1704-1807-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5116.05</v>
+        <v>14152.74</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2424-654-CM26</t>
+          <t>1431841-382-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3408.37</v>
+        <v>1647.67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2427-433-CM26</t>
+          <t>2424-580-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>6213.9</v>
+        <v>23864.89</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>316-299-CM26</t>
+          <t>4968-718-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4071,22 +4071,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>12587.23</v>
+        <v>1300.85</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4105-346-CM26</t>
+          <t>2428-472-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,22 +4132,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4767.68</v>
+        <v>5116.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3333-218-CM26</t>
+          <t>2424-654-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4188,27 +4188,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.061.200-3</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLMUE</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11166.4</v>
+        <v>3408.37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2426-34-CM26</t>
+          <t>316-299-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4279,32 +4279,28 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>763566.01</v>
+        <v>12587.23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3776-298-CM26</t>
+          <t>4105-346-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4314,27 +4310,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4344,12 +4340,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4359,13 +4355,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8725.790000000001</v>
+        <v>4767.68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3776-311-CM26</t>
+          <t>2427-433-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4375,27 +4371,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4405,12 +4401,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4420,13 +4416,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2117.2</v>
+        <v>6213.9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3047-297-CM26</t>
+          <t>3333-218-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4441,22 +4437,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4466,12 +4462,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4481,13 +4477,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6056.65</v>
+        <v>11166.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1285502-18-SE26</t>
+          <t>2426-34-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4502,7 +4498,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4512,12 +4508,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4527,12 +4523,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4546,13 +4542,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3276.94</v>
+        <v>763566.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4968-867-CM26</t>
+          <t>3776-298-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4567,7 +4563,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4577,12 +4573,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4592,12 +4588,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4607,13 +4603,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1307.11</v>
+        <v>8725.790000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>898-2056-CM26</t>
+          <t>3776-311-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4628,7 +4624,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4638,12 +4634,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4653,12 +4649,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4668,13 +4664,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>271.2</v>
+        <v>2117.2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1285502-19-SE26</t>
+          <t>3047-297-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4689,22 +4685,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>Academia Politécnica Naval</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4714,32 +4710,28 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3251.16</v>
+        <v>6056.65</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3596-479-CM26</t>
+          <t>1285502-18-SE26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4754,7 +4746,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4764,12 +4756,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4779,28 +4771,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3194.81</v>
+        <v>3276.94</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3232-443-CM26</t>
+          <t>4968-867-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4810,12 +4806,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4825,12 +4821,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4840,12 +4836,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4855,13 +4851,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>8572.4</v>
+        <v>1307.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2424-907-CM26</t>
+          <t>898-2056-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4871,27 +4867,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4901,12 +4897,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4916,13 +4912,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10511.13</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3776-370-CM26</t>
+          <t>3596-479-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4932,27 +4928,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4962,12 +4958,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4977,13 +4973,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5095.46</v>
+        <v>3194.81</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3776-369-CM26</t>
+          <t>1285502-19-SE26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4993,27 +4989,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5023,28 +5019,32 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4099.74</v>
+        <v>3251.16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3882-277-CM26</t>
+          <t>3232-443-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1426.9</v>
+        <v>8572.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2424-917-CM26</t>
+          <t>2424-907-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>10032.31</v>
+        <v>10511.13</v>
       </c>
     </row>
     <row r="78">
@@ -5288,7 +5288,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2698-175-CM26</t>
+          <t>2424-917-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5343,13 +5343,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>6937.6</v>
+        <v>10032.31</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4968-1056-CM26</t>
+          <t>3882-277-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5404,13 +5404,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1092.62</v>
+        <v>1426.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2428-765-CM26</t>
+          <t>3776-369-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3314.2</v>
+        <v>4099.74</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2211-673-CM26</t>
+          <t>3776-370-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5486,22 +5486,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5526,13 +5526,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2368.47</v>
+        <v>5095.46</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2424-927-CM26</t>
+          <t>2698-175-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5587,13 +5587,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>19759.47</v>
+        <v>6937.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2755-285-CM26</t>
+          <t>4968-1056-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5613,17 +5613,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5648,13 +5648,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1748.08</v>
+        <v>1092.62</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1431841-785-CM26</t>
+          <t>2428-765-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5709,13 +5709,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>390.81</v>
+        <v>3314.2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1431841-784-CM26</t>
+          <t>2211-673-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5730,22 +5730,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5770,13 +5770,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5376.88</v>
+        <v>2368.47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1431841-789-CM26</t>
+          <t>2424-927-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5831,13 +5831,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1794.53</v>
+        <v>19759.47</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4301-480-CM26</t>
+          <t>2755-285-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5892,13 +5892,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2923.96</v>
+        <v>1748.08</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2698-178-CM26</t>
+          <t>1431841-785-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5913,22 +5913,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5953,13 +5953,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>7062.75</v>
+        <v>390.81</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3882-283-CM26</t>
+          <t>1431841-784-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5984,12 +5984,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>37791.67</v>
+        <v>5376.88</v>
       </c>
     </row>
     <row r="92">
@@ -6081,7 +6081,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2424-938-CM26</t>
+          <t>2755-286-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6101,17 +6101,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6136,13 +6136,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>9053.4</v>
+        <v>17226.36</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2755-286-CM26</t>
+          <t>2424-938-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6162,17 +6162,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>17226.36</v>
+        <v>9053.4</v>
       </c>
     </row>
     <row r="95">
@@ -6264,7 +6264,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1431841-791-CM26</t>
+          <t>3882-283-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6319,13 +6319,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2170.14</v>
+        <v>37791.67</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3515-329-CM26</t>
+          <t>4301-480-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6380,13 +6380,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3581.02</v>
+        <v>2923.96</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2737-451-CM26</t>
+          <t>2698-178-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6401,22 +6401,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>16564.59</v>
+        <v>7062.75</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4301-489-CM26</t>
+          <t>1431841-789-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6462,22 +6462,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6502,13 +6502,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1649.2</v>
+        <v>1794.53</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1134432-525-CM26</t>
+          <t>1431841-791-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6563,13 +6563,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>650.48</v>
+        <v>2170.14</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2698-179-CM26</t>
+          <t>3515-329-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6624,13 +6624,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1115.07</v>
+        <v>3581.02</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4105-481-CM26</t>
+          <t>2737-451-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6645,22 +6645,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6685,13 +6685,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4637.43</v>
+        <v>16564.59</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3776-376-CM26</t>
+          <t>3776-377-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>6122.19</v>
+        <v>25782.06</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3776-377-CM26</t>
+          <t>4301-489-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6772,17 +6772,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6807,13 +6807,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>25782.06</v>
+        <v>1649.2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4964-63-CM26</t>
+          <t>2698-179-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6868,13 +6868,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10903.19</v>
+        <v>1115.07</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3232-485-CM26</t>
+          <t>4105-481-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6929,13 +6929,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3435.45</v>
+        <v>4637.43</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2799-706-CM26</t>
+          <t>3776-376-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6950,22 +6950,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6975,12 +6975,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7534.8</v>
+        <v>6122.19</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2427-650-CM26</t>
+          <t>1134432-525-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7051,13 +7051,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>22349.47</v>
+        <v>650.48</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1431841-836-CM26</t>
+          <t>4964-63-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7097,12 +7097,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7112,13 +7112,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10311.77</v>
+        <v>10903.19</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3776-392-CM26</t>
+          <t>3232-485-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>16120.52</v>
+        <v>3435.45</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2799-739-CM26</t>
+          <t>2799-706-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7234,13 +7234,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>816.71</v>
+        <v>7534.8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2424-1001-CM26</t>
+          <t>2427-650-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7295,13 +7295,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>20338.4</v>
+        <v>22349.47</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>574-270-CM26</t>
+          <t>1431841-836-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.606.610-2</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7356,13 +7356,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>594.1900000000001</v>
+        <v>10311.77</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3596-606-CM26</t>
+          <t>3776-392-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7372,27 +7372,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7417,13 +7417,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2636.97</v>
+        <v>16120.52</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1285502-21-CM26</t>
+          <t>2799-739-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7433,27 +7433,27 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.000.258-5</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7478,13 +7478,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5239.55</v>
+        <v>816.71</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3381-193-CM26</t>
+          <t>2424-1001-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7494,27 +7494,27 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>75.245.100-1</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7539,6 +7539,250 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
+        <v>20338.4</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>574-270-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>61.606.610-2</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>594.1900000000001</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3596-606-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>69.050.300-K</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>2636.97</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1285502-21-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>69.061.400-6</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>76.000.258-5</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>5239.55</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>3381-193-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>75.245.100-1</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
         <v>2113.63</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M216"/>
+  <dimension ref="A1:M214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2428-68-CM25</t>
+          <t>3776-66-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.238.721-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6342.04</v>
+        <v>8146.78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3776-66-CM25</t>
+          <t>2428-68-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8146.78</v>
+        <v>6342.04</v>
       </c>
     </row>
     <row r="12">
@@ -4666,7 +4666,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2737-546-CM25</t>
+          <t>2737-547-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>619.76</v>
+        <v>2979.88</v>
       </c>
     </row>
     <row r="71">
@@ -4788,7 +4788,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2737-547-CM25</t>
+          <t>316-505-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2979.88</v>
+        <v>3188.05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>316-505-CM25</t>
+          <t>2737-546-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3188.05</v>
+        <v>619.76</v>
       </c>
     </row>
     <row r="74">
@@ -5951,7 +5951,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3776-636-CM25</t>
+          <t>2737-733-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6006,13 +6006,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>10602.3</v>
+        <v>3225.85</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2737-733-CM25</t>
+          <t>3776-636-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3225.85</v>
+        <v>10602.3</v>
       </c>
     </row>
     <row r="93">
@@ -6317,7 +6317,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3333-431-CM25</t>
+          <t>2698-307-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.061.200-3</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLMUE</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>AGROINDUSTRIAS DEL SUR SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.359.833-0</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6372,13 +6372,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5273</v>
+        <v>7102.91</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2698-307-CM25</t>
+          <t>3333-431-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>AGROINDUSTRIAS DEL SUR SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>76.359.833-0</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>7102.91</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="99">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6744,7 +6744,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1431841-564-CM25</t>
+          <t>1704-7066-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6784,32 +6784,28 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>91202.3</v>
+        <v>6068.95</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1704-7066-CM25</t>
+          <t>316-963-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6829,17 +6825,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6849,12 +6845,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6864,13 +6860,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6068.95</v>
+        <v>3330.93</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>316-963-CM25</t>
+          <t>4301-4125-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6895,12 +6891,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6910,12 +6906,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA SIBESA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.126.547-4</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6925,13 +6921,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3330.93</v>
+        <v>526.25</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4301-4125-CM25</t>
+          <t>3086-15-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6941,27 +6937,27 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.102.005-8</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6971,12 +6967,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6986,13 +6982,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>526.25</v>
+        <v>2415.14</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3086-15-CM26</t>
+          <t>3086-14-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7022,7 +7018,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7032,12 +7028,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7047,13 +7043,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2415.14</v>
+        <v>7457.36</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3086-14-CM26</t>
+          <t>4968-60-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7078,12 +7074,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.102.005-8</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7093,12 +7089,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7108,13 +7104,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>7457.36</v>
+        <v>495.2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4968-60-CM26</t>
+          <t>4964-5-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7129,7 +7125,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7139,12 +7135,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7154,12 +7150,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7169,13 +7165,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>495.2</v>
+        <v>11010.29</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2945-17-CM26</t>
+          <t>3776-34-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7190,22 +7186,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.102.004-K</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7215,12 +7211,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7230,13 +7226,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>991.4299999999999</v>
+        <v>9291.32</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4964-5-CM26</t>
+          <t>2594-113-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7251,7 +7247,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7261,12 +7257,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7276,12 +7272,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7291,13 +7287,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>11010.29</v>
+        <v>27740.53</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3776-34-CM26</t>
+          <t>3333-66-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7307,27 +7303,27 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7337,12 +7333,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>AGROINDUSTRIAS DEL SUR SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.359.833-0</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7352,13 +7348,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>9291.32</v>
+        <v>11634.27</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2594-113-CM26</t>
+          <t>1048-51-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7368,12 +7364,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7383,12 +7379,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7398,12 +7394,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.292.846-7</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7413,13 +7409,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>27740.53</v>
+        <v>508.62</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3333-66-CM26</t>
+          <t>1134432-116-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7434,22 +7430,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.061.200-3</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLMUE</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7459,12 +7455,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>AGROINDUSTRIAS DEL SUR SPA</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.359.833-0</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7474,13 +7470,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>11634.27</v>
+        <v>2896.03</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1048-51-CM26</t>
+          <t>2755-37-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7495,22 +7491,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7520,12 +7516,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA GASSET DEL VALLE SPA</t>
+          <t>RASTRO RETAIL SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.292.846-7</t>
+          <t>77.888.564-6</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7535,13 +7531,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>508.62</v>
+        <v>1363.57</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1134432-116-CM26</t>
+          <t>2755-38-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7561,17 +7557,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7581,12 +7577,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7596,13 +7592,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2896.03</v>
+        <v>2773.59</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2755-37-CM26</t>
+          <t>2211-189-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7617,7 +7613,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7627,12 +7623,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7642,12 +7638,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>RASTRO RETAIL SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.888.564-6</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7657,13 +7653,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1363.57</v>
+        <v>13124.76</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2755-38-CM26</t>
+          <t>2698-29-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7678,7 +7674,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7688,12 +7684,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7703,12 +7699,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>CONSTRUCTORA SIBESA SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>76.126.547-4</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7718,13 +7714,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2773.59</v>
+        <v>1862.63</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2211-189-CM26</t>
+          <t>1499899-51-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7739,22 +7735,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7764,12 +7760,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>ANA ISABEL MARIAN BAHAMONDES</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>10.991.344-8</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7779,13 +7775,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>13124.76</v>
+        <v>3549.12</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2698-29-CM26</t>
+          <t>3232-119-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7795,27 +7791,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7825,12 +7821,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA SIBESA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.126.547-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7840,13 +7836,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1862.63</v>
+        <v>7931.01</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1499899-51-CM26</t>
+          <t>316-131-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7856,27 +7852,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7886,12 +7882,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>ANA ISABEL MARIAN BAHAMONDES</t>
+          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>10.991.344-8</t>
+          <t>76.000.258-5</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7901,13 +7897,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3549.12</v>
+        <v>21240.17</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2945-141-CM26</t>
+          <t>4105-152-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7917,27 +7913,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.102.004-K</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7947,12 +7943,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7962,13 +7958,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>9012.629999999999</v>
+        <v>4766.9</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3232-119-CM26</t>
+          <t>2783-243-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7983,22 +7979,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8008,12 +8004,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8023,13 +8019,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>7931.01</v>
+        <v>6719.46</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>316-131-CM26</t>
+          <t>2783-253-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8044,7 +8040,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8054,12 +8050,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8069,12 +8065,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.000.258-5</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8084,13 +8080,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>21240.17</v>
+        <v>2815.78</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4105-152-CM26</t>
+          <t>2428-193-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8105,7 +8101,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8115,12 +8111,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8130,12 +8126,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8145,13 +8141,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4766.9</v>
+        <v>5190.41</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2783-243-CM26</t>
+          <t>1943-65-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8166,22 +8162,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8206,13 +8202,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>6719.46</v>
+        <v>14370.17</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2783-253-CM26</t>
+          <t>1285502-5-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8227,22 +8223,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8252,12 +8248,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8267,13 +8263,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2815.78</v>
+        <v>328.12</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2428-193-CM26</t>
+          <t>3446-42-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8283,12 +8279,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8298,12 +8294,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8313,12 +8309,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SERVIVAC INTERNATIONAL</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.971.640-2</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8328,13 +8324,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5190.41</v>
+        <v>15184.41</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1943-65-CM26</t>
+          <t>574-131-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8344,12 +8340,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8359,12 +8355,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.610-2</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8374,12 +8370,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8389,13 +8385,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>14370.17</v>
+        <v>338.63</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1285502-5-CM26</t>
+          <t>1079516-309-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8405,12 +8401,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8420,12 +8416,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8435,12 +8431,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8450,13 +8446,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>328.12</v>
+        <v>4529.89</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3446-42-CM26</t>
+          <t>1079516-310-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8471,7 +8467,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8481,12 +8477,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8496,12 +8492,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SERVIVAC INTERNATIONAL</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.971.640-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8511,13 +8507,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>15184.41</v>
+        <v>4235.01</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>574-131-CM26</t>
+          <t>4964-25-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8532,7 +8528,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8542,12 +8538,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.606.610-2</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8572,13 +8568,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>338.63</v>
+        <v>11467.05</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1079516-309-CM26</t>
+          <t>2799-417-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8593,7 +8589,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8603,12 +8599,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8618,12 +8614,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8633,13 +8629,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>4529.89</v>
+        <v>283.43</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1079516-310-CM26</t>
+          <t>3776-217-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8654,7 +8650,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8664,12 +8660,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8679,12 +8675,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8694,13 +8690,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>4235.01</v>
+        <v>9010.549999999999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4964-25-CM26</t>
+          <t>4964-27-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8715,7 +8711,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8755,13 +8751,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>11467.05</v>
+        <v>673.14</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2799-417-CM26</t>
+          <t>3596-299-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8776,7 +8772,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8786,12 +8782,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8816,13 +8812,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>283.43</v>
+        <v>3212.75</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4964-27-CM26</t>
+          <t>2698-95-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8837,7 +8833,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8847,12 +8843,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8862,12 +8858,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8877,13 +8873,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>673.14</v>
+        <v>3847.53</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3776-217-CM26</t>
+          <t>1285502-10-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8898,7 +8894,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8908,12 +8904,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8923,12 +8919,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8938,13 +8934,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>9010.549999999999</v>
+        <v>538.6799999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3596-299-CM26</t>
+          <t>4301-271-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8954,12 +8950,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8969,12 +8965,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8999,13 +8995,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3212.75</v>
+        <v>972.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2698-95-CM26</t>
+          <t>1704-1807-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9015,27 +9011,27 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9045,12 +9041,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9060,13 +9056,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3847.53</v>
+        <v>14152.74</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1285502-10-CM26</t>
+          <t>2424-580-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9076,12 +9072,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9091,12 +9087,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9106,12 +9102,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9121,13 +9117,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>538.6799999999999</v>
+        <v>23864.89</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4301-271-CM26</t>
+          <t>4968-718-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9142,7 +9138,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9152,12 +9148,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9167,12 +9163,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9182,13 +9178,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>972.5</v>
+        <v>1300.85</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1704-1807-CM26</t>
+          <t>2428-472-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9203,7 +9199,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9213,12 +9209,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9228,12 +9224,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9243,13 +9239,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>14152.74</v>
+        <v>5116.05</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1431841-382-CM26</t>
+          <t>2424-654-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9264,7 +9260,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9274,12 +9270,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9289,12 +9285,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9304,13 +9300,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1647.67</v>
+        <v>3408.37</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2424-580-CM26</t>
+          <t>2427-433-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9325,22 +9321,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9350,12 +9346,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9365,13 +9361,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>23864.89</v>
+        <v>6213.9</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4968-718-CM26</t>
+          <t>316-299-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9386,22 +9382,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9411,12 +9407,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9426,13 +9422,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1300.85</v>
+        <v>12587.23</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2428-472-CM26</t>
+          <t>4105-346-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9447,22 +9443,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9472,12 +9468,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9487,13 +9483,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>5116.05</v>
+        <v>4767.68</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2424-654-CM26</t>
+          <t>3333-218-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9503,27 +9499,27 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9533,12 +9529,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9548,13 +9544,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3408.37</v>
+        <v>11166.4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>316-299-CM26</t>
+          <t>2426-34-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9564,12 +9560,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9579,12 +9575,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9594,28 +9590,32 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>12587.23</v>
+        <v>763566.01</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4105-346-CM26</t>
+          <t>3776-298-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9625,27 +9625,27 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9655,12 +9655,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9670,13 +9670,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4767.68</v>
+        <v>8725.790000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2427-433-CM26</t>
+          <t>3776-311-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9686,27 +9686,27 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9731,13 +9731,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>6213.9</v>
+        <v>2117.2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3333-218-CM26</t>
+          <t>3047-297-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9752,22 +9752,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>69.061.200-3</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLMUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9792,13 +9792,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>11166.4</v>
+        <v>6056.65</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2426-34-CM26</t>
+          <t>1285502-18-SE26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9823,12 +9823,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9838,12 +9838,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9857,13 +9857,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>763566.01</v>
+        <v>3276.94</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3776-298-CM26</t>
+          <t>4968-867-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9918,13 +9918,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>8725.790000000001</v>
+        <v>1307.11</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3776-311-CM26</t>
+          <t>898-2056-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9979,13 +9979,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2117.2</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3047-297-CM26</t>
+          <t>1285502-19-SE26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10000,22 +10000,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10025,28 +10025,32 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>6056.65</v>
+        <v>3251.16</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1285502-18-SE26</t>
+          <t>3596-479-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10061,7 +10065,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10071,12 +10075,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10086,32 +10090,28 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3276.94</v>
+        <v>3194.81</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4968-867-CM26</t>
+          <t>3232-443-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10121,12 +10121,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10136,12 +10136,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10151,12 +10151,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10166,13 +10166,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1307.11</v>
+        <v>8572.4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>898-2056-CM26</t>
+          <t>2424-907-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10182,27 +10182,27 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10212,12 +10212,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10227,13 +10227,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>271.2</v>
+        <v>10511.13</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1285502-19-SE26</t>
+          <t>3776-369-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10243,27 +10243,27 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10273,32 +10273,28 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3251.16</v>
+        <v>4099.74</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3596-479-CM26</t>
+          <t>3776-370-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10308,27 +10304,27 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10338,12 +10334,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10353,13 +10349,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3194.81</v>
+        <v>5095.46</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3232-443-CM26</t>
+          <t>3882-277-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10374,7 +10370,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10384,12 +10380,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10399,12 +10395,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10414,13 +10410,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8572.4</v>
+        <v>1426.9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2424-907-CM26</t>
+          <t>2755-280-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10435,7 +10431,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10445,12 +10441,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10460,12 +10456,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10475,13 +10471,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>10511.13</v>
+        <v>1056.89</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2755-280-CM26</t>
+          <t>4548-435-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10506,12 +10502,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10521,12 +10517,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10536,13 +10532,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1056.89</v>
+        <v>3865.17</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4548-435-CM26</t>
+          <t>2424-917-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10567,12 +10563,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10582,12 +10578,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10597,13 +10593,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3865.17</v>
+        <v>10032.31</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2424-917-CM26</t>
+          <t>4968-1056-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10618,22 +10614,22 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10643,12 +10639,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10658,13 +10654,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10032.31</v>
+        <v>1092.62</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3882-277-CM26</t>
+          <t>2428-765-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10679,7 +10675,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10689,12 +10685,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10704,12 +10700,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10719,13 +10715,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1426.9</v>
+        <v>3314.2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3776-369-CM26</t>
+          <t>2211-673-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10740,22 +10736,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10765,12 +10761,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10780,13 +10776,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4099.74</v>
+        <v>2368.47</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3776-370-CM26</t>
+          <t>2424-927-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10801,7 +10797,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10811,12 +10807,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10826,12 +10822,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10841,13 +10837,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>5095.46</v>
+        <v>19759.47</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4968-1056-CM26</t>
+          <t>2698-175-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10867,17 +10863,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10887,12 +10883,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10902,13 +10898,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1092.62</v>
+        <v>6937.6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2428-765-CM26</t>
+          <t>2755-285-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10928,17 +10924,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10948,12 +10944,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10963,13 +10959,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3314.2</v>
+        <v>1748.08</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2211-673-CM26</t>
+          <t>1431841-784-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10984,22 +10980,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11009,12 +11005,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11024,13 +11020,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2368.47</v>
+        <v>5376.88</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2424-927-CM26</t>
+          <t>2698-178-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11045,22 +11041,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11070,12 +11066,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11085,13 +11081,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>19759.47</v>
+        <v>7062.75</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2698-175-CM26</t>
+          <t>4301-480-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11106,7 +11102,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11116,12 +11112,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11131,12 +11127,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11146,13 +11142,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>6937.6</v>
+        <v>2923.96</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2755-285-CM26</t>
+          <t>3882-283-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11167,22 +11163,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11192,12 +11188,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11207,13 +11203,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1748.08</v>
+        <v>37791.67</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1431841-785-CM26</t>
+          <t>2755-286-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11228,22 +11224,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11253,12 +11249,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11268,13 +11264,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>390.81</v>
+        <v>17226.36</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1431841-784-CM26</t>
+          <t>2424-938-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11289,7 +11285,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11299,12 +11295,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11314,12 +11310,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11329,7 +11325,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5376.88</v>
+        <v>9053.4</v>
       </c>
     </row>
     <row r="179">
@@ -11396,7 +11392,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2755-286-CM26</t>
+          <t>4548-437-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11421,12 +11417,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11436,12 +11432,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11451,13 +11447,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>17226.36</v>
+        <v>9464.540000000001</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2424-938-CM26</t>
+          <t>1431841-791-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11472,7 +11468,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11482,12 +11478,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11497,12 +11493,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11512,13 +11508,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>9053.4</v>
+        <v>2170.14</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4548-437-CM26</t>
+          <t>3515-329-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11533,7 +11529,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11543,12 +11539,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11558,12 +11554,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11573,13 +11569,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>9464.540000000001</v>
+        <v>3581.02</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3882-283-CM26</t>
+          <t>2737-451-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11594,7 +11590,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11604,12 +11600,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11619,12 +11615,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11634,13 +11630,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>37791.67</v>
+        <v>16564.59</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4301-480-CM26</t>
+          <t>2698-179-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11655,7 +11651,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11665,12 +11661,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11680,12 +11676,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11695,13 +11691,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2923.96</v>
+        <v>1115.07</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2698-178-CM26</t>
+          <t>1134432-525-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11716,22 +11712,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11741,12 +11737,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11756,13 +11752,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>7062.75</v>
+        <v>650.48</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1431841-789-CM26</t>
+          <t>4301-489-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11777,22 +11773,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11802,12 +11798,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11817,13 +11813,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1794.53</v>
+        <v>1649.2</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1431841-791-CM26</t>
+          <t>4105-481-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11838,22 +11834,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11863,12 +11859,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11878,13 +11874,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2170.14</v>
+        <v>4637.43</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3515-329-CM26</t>
+          <t>3776-376-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11899,22 +11895,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11924,12 +11920,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11939,13 +11935,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3581.02</v>
+        <v>6122.19</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2737-451-CM26</t>
+          <t>3776-377-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11960,7 +11956,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11970,12 +11966,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11985,12 +11981,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -12000,13 +11996,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>16564.59</v>
+        <v>25782.06</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2698-179-CM26</t>
+          <t>4964-63-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12021,7 +12017,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12031,12 +12027,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12046,12 +12042,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12061,13 +12057,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1115.07</v>
+        <v>10903.19</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4301-489-CM26</t>
+          <t>3232-485-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12082,22 +12078,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12107,12 +12103,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12122,13 +12118,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1649.2</v>
+        <v>3435.45</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1134432-525-CM26</t>
+          <t>2799-706-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12143,7 +12139,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12153,12 +12149,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12168,12 +12164,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12183,13 +12179,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>650.48</v>
+        <v>7534.8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3776-376-CM26</t>
+          <t>2427-650-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12204,22 +12200,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12229,12 +12225,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12244,13 +12240,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>6122.19</v>
+        <v>22349.47</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4105-481-CM26</t>
+          <t>3776-392-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12265,22 +12261,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12290,12 +12286,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12305,13 +12301,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4637.43</v>
+        <v>16120.52</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3776-377-CM26</t>
+          <t>2799-739-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12326,22 +12322,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12366,13 +12362,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>25782.06</v>
+        <v>816.71</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4964-63-CM26</t>
+          <t>2424-1001-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12387,7 +12383,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12397,12 +12393,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12412,12 +12408,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12427,13 +12423,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>10903.19</v>
+        <v>20338.4</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3232-485-CM26</t>
+          <t>574-270-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12448,22 +12444,22 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>61.606.610-2</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12473,12 +12469,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12488,13 +12484,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3435.45</v>
+        <v>594.1900000000001</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2799-706-CM26</t>
+          <t>3596-606-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12504,27 +12500,27 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12534,12 +12530,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12549,13 +12545,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>7534.8</v>
+        <v>2636.97</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2427-650-CM26</t>
+          <t>4301-531-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12565,12 +12561,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12580,12 +12576,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12595,12 +12591,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12610,13 +12606,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>22349.47</v>
+        <v>4928.24</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1431841-836-CM26</t>
+          <t>1285502-21-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12626,27 +12622,27 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12656,12 +12652,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.000.258-5</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12671,13 +12667,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>10311.77</v>
+        <v>5239.55</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3776-392-CM26</t>
+          <t>2945-631-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12687,12 +12683,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12702,12 +12698,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.102.004-K</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12717,12 +12713,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12732,13 +12728,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>16120.52</v>
+        <v>3912.34</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2799-739-CM26</t>
+          <t>4964-70-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12748,27 +12744,27 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12793,13 +12789,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>816.71</v>
+        <v>869.21</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2424-1001-CM26</t>
+          <t>2428-850-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12809,27 +12805,27 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12839,12 +12835,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12854,13 +12850,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>20338.4</v>
+        <v>5079.52</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>574-270-CM26</t>
+          <t>1704-4562-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12870,27 +12866,27 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.606.610-2</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12900,12 +12896,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12915,13 +12911,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>594.1900000000001</v>
+        <v>10307.89</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3596-606-CM26</t>
+          <t>3232-569-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12936,7 +12932,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12946,12 +12942,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12961,12 +12957,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12976,13 +12972,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2636.97</v>
+        <v>8638.57</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4301-531-CM26</t>
+          <t>4964-86-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12997,22 +12993,22 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13022,12 +13018,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>HERALDO CASTRO PALMA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>6.092.291-8</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13037,13 +13033,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4928.24</v>
+        <v>1744.93</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1285502-21-CM26</t>
+          <t>3381-193-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13058,7 +13054,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13068,12 +13064,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>75.245.100-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13083,12 +13079,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.000.258-5</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13098,13 +13094,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>5239.55</v>
+        <v>2113.63</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2945-631-CM26</t>
+          <t>3232-575-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13119,22 +13115,22 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.102.004-K</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13144,12 +13140,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13159,13 +13155,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>3912.34</v>
+        <v>7388.22</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4964-70-CM26</t>
+          <t>2427-791-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13180,7 +13176,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13190,12 +13186,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13205,12 +13201,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13220,13 +13216,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>869.21</v>
+        <v>28343.92</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2428-850-CM26</t>
+          <t>608-10183-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13236,27 +13232,27 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13266,12 +13262,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13281,13 +13277,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>5079.52</v>
+        <v>27445.8</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1704-4562-CM26</t>
+          <t>3596-761-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13297,27 +13293,27 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13327,12 +13323,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13342,13 +13338,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>10307.89</v>
+        <v>4701.15</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3232-569-CM26</t>
+          <t>4105-623-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13358,27 +13354,27 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13388,12 +13384,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13403,13 +13399,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>8638.57</v>
+        <v>4616.79</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>4964-86-CM26</t>
+          <t>3776-478-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13419,12 +13415,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13434,12 +13430,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13449,12 +13445,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>HERALDO CASTRO PALMA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>6.092.291-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13464,13 +13460,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1744.93</v>
+        <v>31922.5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3381-193-CM26</t>
+          <t>3333-342-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13480,27 +13476,27 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>75.245.100-1</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13510,12 +13506,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13525,129 +13521,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2113.63</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>3232-575-CM26</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>69.073.500-8</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M215" s="2" t="n">
-        <v>7388.22</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2427-791-CM26</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>69.060.900-2</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M216" s="2" t="n">
-        <v>28343.92</v>
+        <v>3122.61</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
@@ -623,7 +623,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1891,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1956,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2021,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2208,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2273,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2338,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2403,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2468,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2533,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2659,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2724,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2789,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2854,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2919,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3106,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3171,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3297,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3423,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3610,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3675,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3740,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3805,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3931,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +3996,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4122,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4248,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4313,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4378,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4443,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4508,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4573,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4638,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4703,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4768,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4894,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +4959,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5085,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5394,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5459,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5572,7 +5772,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5694,7 +5898,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5816,7 +6024,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5877,7 +6089,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5938,7 +6154,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5999,7 +6219,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6060,7 +6284,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6121,7 +6349,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6182,7 +6414,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6243,7 +6479,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6304,7 +6544,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6426,7 +6670,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6487,7 +6735,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6548,7 +6800,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6670,7 +6926,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6914,7 +7174,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6975,7 +7239,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7426,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7219,7 +7491,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7280,7 +7556,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7341,7 +7621,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7524,7 +7808,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7646,7 +7934,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8121,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8373,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8438,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8564,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8378,7 +8690,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8755,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8500,7 +8820,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8561,7 +8885,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8622,7 +8950,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8683,7 +9015,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +9080,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8805,7 +9145,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8866,7 +9210,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8927,7 +9275,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8988,7 +9340,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9466,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9531,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9232,7 +9596,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9293,7 +9661,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9354,7 +9726,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9415,7 +9791,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9476,7 +9856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9537,7 +9921,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9663,7 +10051,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9785,7 +10177,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9911,7 +10307,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10098,7 +10498,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10220,7 +10624,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10342,7 +10750,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10586,7 +10998,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10647,7 +11063,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10708,7 +11128,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10830,7 +11254,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10891,7 +11319,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11013,7 +11445,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11135,7 +11571,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11196,7 +11636,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11257,7 +11701,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11318,7 +11766,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11501,7 +11953,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11806,7 +12262,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11867,7 +12327,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11989,7 +12453,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12050,7 +12518,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12111,7 +12583,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12172,7 +12648,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12233,7 +12713,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12294,7 +12778,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12355,7 +12843,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12477,7 +12969,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12538,7 +13034,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12599,7 +13099,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12782,7 +13286,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12843,7 +13351,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13148,7 +13660,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13270,7 +13786,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13331,7 +13851,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13392,7 +13916,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13453,7 +13981,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13514,7 +14046,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M214"/>
+  <dimension ref="A1:M220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1022,7 +1022,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3776-66-CM25</t>
+          <t>2737-75-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8146.78</v>
+        <v>3043.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2428-68-CM25</t>
+          <t>3776-66-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1127,28 +1127,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.238.721-2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6342.04</v>
+        <v>8146.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2737-75-CM25</t>
+          <t>2428-68-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1168,17 +1172,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1188,26 +1192,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.238.721-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3043.4</v>
+        <v>6342.04</v>
       </c>
     </row>
     <row r="13">
@@ -1339,7 +1339,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2945-77-CM25</t>
+          <t>1134432-66-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.102.004-K</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ALIMENTOS, NUTRIENTES E INSUMO</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.086.115-4</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7125.45</v>
+        <v>4434.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1134432-66-CM25</t>
+          <t>2945-77-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.102.004-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
+          <t>COMERCIALIZADORA DE ALIMENTOS, NUTRIENTES E INSUMO</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.238.721-2</t>
+          <t>76.086.115-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4434.13</v>
+        <v>7125.45</v>
       </c>
     </row>
     <row r="17">
@@ -2290,7 +2290,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1704-1778-CM25</t>
+          <t>2755-140-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2310,17 +2310,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5522.86</v>
+        <v>3927.91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2755-140-CM25</t>
+          <t>1704-1778-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>FIRAMCO SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.942.697-1</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3927.91</v>
+        <v>5522.86</v>
       </c>
     </row>
     <row r="32">
@@ -3375,7 +3375,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2427-633-CM25</t>
+          <t>3882-184-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3415,32 +3415,28 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4167.01</v>
+        <v>1160.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3882-184-CM25</t>
+          <t>4301-347-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3460,17 +3456,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3480,12 +3476,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>Comercializadora TJB S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.095.313-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3495,13 +3491,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1160.31</v>
+        <v>1676.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4301-347-CM25</t>
+          <t>2427-633-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3526,12 +3522,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3541,22 +3537,26 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Comercializadora TJB S.A.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.095.313-k</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1676.25</v>
+        <v>4167.01</v>
       </c>
     </row>
     <row r="50">
@@ -4846,7 +4846,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2737-547-CM25</t>
+          <t>3776-512-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2979.88</v>
+        <v>10524.03</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3776-512-CM25</t>
+          <t>316-505-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4951,32 +4951,28 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>15.775.663-k</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>10524.03</v>
+        <v>3188.05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>316-505-CM25</t>
+          <t>2737-546-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5001,12 +4997,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5016,28 +5012,32 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>15.775.663-k</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3188.05</v>
+        <v>619.76</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2737-546-CM25</t>
+          <t>2737-547-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>619.76</v>
+        <v>2979.88</v>
       </c>
     </row>
     <row r="74">
@@ -5915,7 +5915,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2427-1104-CM25</t>
+          <t>2799-873-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5935,17 +5935,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5955,28 +5955,32 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>13826.45</v>
+        <v>230.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2799-873-CM25</t>
+          <t>2427-1104-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5996,17 +6000,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6016,26 +6020,22 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.209.677-3</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>230.46</v>
+        <v>13826.45</v>
       </c>
     </row>
     <row r="89">
@@ -7256,7 +7256,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3086-14-CM26</t>
+          <t>4968-60-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7281,12 +7281,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.102.005-8</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7457.36</v>
+        <v>495.2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4968-60-CM26</t>
+          <t>3086-14-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.102.005-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7357,12 +7357,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>495.2</v>
+        <v>7457.36</v>
       </c>
     </row>
     <row r="110">
@@ -8199,7 +8199,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4105-152-CM26</t>
+          <t>2783-243-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8219,17 +8219,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8239,32 +8239,28 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4766.9</v>
+        <v>6719.46</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2783-243-CM26</t>
+          <t>4105-152-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8284,17 +8280,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8304,22 +8300,26 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>6719.46</v>
+        <v>4766.9</v>
       </c>
     </row>
     <row r="125">
@@ -8390,7 +8390,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2428-193-CM26</t>
+          <t>1943-65-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8430,32 +8430,28 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>5190.41</v>
+        <v>14370.17</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1943-65-CM26</t>
+          <t>2428-193-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8480,12 +8476,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8495,22 +8491,26 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>14370.17</v>
+        <v>5190.41</v>
       </c>
     </row>
     <row r="128">
@@ -8581,7 +8581,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3446-42-CM26</t>
+          <t>574-131-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.606.610-2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8621,28 +8621,32 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SERVIVAC INTERNATIONAL</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.971.640-2</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>15184.41</v>
+        <v>338.63</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>574-131-CM26</t>
+          <t>3446-42-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8667,12 +8671,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.606.610-2</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8682,26 +8686,22 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SERVIVAC INTERNATIONAL</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.971.640-2</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>338.63</v>
+        <v>15184.41</v>
       </c>
     </row>
     <row r="131">
@@ -8967,7 +8967,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3776-217-CM26</t>
+          <t>4964-27-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9026,13 +9026,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>9010.549999999999</v>
+        <v>673.14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4964-27-CM26</t>
+          <t>3776-217-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9057,12 +9057,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9091,13 +9091,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>673.14</v>
+        <v>9010.549999999999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3596-299-CM26</t>
+          <t>2698-95-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9137,12 +9137,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -9156,13 +9156,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3212.75</v>
+        <v>3847.53</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2698-95-CM26</t>
+          <t>3596-299-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3847.53</v>
+        <v>3212.75</v>
       </c>
     </row>
     <row r="139">
@@ -10068,7 +10068,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3776-311-CM26</t>
+          <t>3047-297-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10108,28 +10108,32 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2117.2</v>
+        <v>6056.65</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3047-297-CM26</t>
+          <t>3776-311-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10154,12 +10158,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10169,26 +10173,22 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>6056.65</v>
+        <v>2117.2</v>
       </c>
     </row>
     <row r="154">
@@ -10259,7 +10259,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4968-867-CM26</t>
+          <t>898-2056-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10299,32 +10299,28 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1307.11</v>
+        <v>271.2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>898-2056-CM26</t>
+          <t>4968-867-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10349,12 +10345,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10364,28 +10360,32 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>271.2</v>
+        <v>1307.11</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1285502-19-SE26</t>
+          <t>3596-479-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10444,13 +10444,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3251.16</v>
+        <v>3194.81</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3596-479-CM26</t>
+          <t>1285502-19-SE26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3194.81</v>
+        <v>3251.16</v>
       </c>
     </row>
     <row r="159">
@@ -10641,7 +10641,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3776-369-CM26</t>
+          <t>3882-277-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10696,13 +10696,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4099.74</v>
+        <v>1426.9</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3776-370-CM26</t>
+          <t>2755-280-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10722,17 +10722,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10742,32 +10742,28 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIAL ANDES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.765.995-2</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>5095.46</v>
+        <v>1056.89</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3882-277-CM26</t>
+          <t>4548-435-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10787,17 +10783,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10807,12 +10803,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10822,13 +10818,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1426.9</v>
+        <v>3865.17</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2755-280-CM26</t>
+          <t>2424-917-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10853,12 +10849,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10868,28 +10864,32 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>77.801.815-2</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1056.89</v>
+        <v>10032.31</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4548-435-CM26</t>
+          <t>3776-370-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10909,17 +10909,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10929,28 +10929,32 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>77.765.995-2</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3865.17</v>
+        <v>5095.46</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2424-917-CM26</t>
+          <t>3776-369-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10970,17 +10974,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10990,32 +10994,28 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>10032.31</v>
+        <v>4099.74</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4968-1056-CM26</t>
+          <t>2755-285-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11035,17 +11035,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11055,32 +11055,28 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1092.62</v>
+        <v>1748.08</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2428-765-CM26</t>
+          <t>2698-175-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11100,17 +11096,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11139,13 +11135,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3314.2</v>
+        <v>6937.6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2211-673-CM26</t>
+          <t>2424-927-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11165,17 +11161,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.061.100-7</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11185,28 +11181,32 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>77.801.815-2</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2368.47</v>
+        <v>19759.47</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2424-927-CM26</t>
+          <t>2211-673-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11226,17 +11226,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11246,32 +11246,28 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.029.126-9</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>19759.47</v>
+        <v>2368.47</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2698-175-CM26</t>
+          <t>4968-1056-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11291,17 +11287,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11311,17 +11307,17 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11330,13 +11326,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6937.6</v>
+        <v>1092.62</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2755-285-CM26</t>
+          <t>2428-765-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11356,17 +11352,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11376,22 +11372,26 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1748.08</v>
+        <v>3314.2</v>
       </c>
     </row>
     <row r="173">
@@ -11462,7 +11462,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2698-178-CM26</t>
+          <t>2424-938-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11482,17 +11482,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11502,28 +11502,32 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+          <t>77.801.815-2</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>7062.75</v>
+        <v>9053.4</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4301-480-CM26</t>
+          <t>2755-286-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11548,12 +11552,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11563,12 +11567,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11582,13 +11586,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2923.96</v>
+        <v>17226.36</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3882-283-CM26</t>
+          <t>4548-437-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11608,17 +11612,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11628,32 +11632,28 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>37791.67</v>
+        <v>9464.540000000001</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2755-286-CM26</t>
+          <t>3882-283-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11673,17 +11673,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11693,12 +11693,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11712,13 +11712,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>17226.36</v>
+        <v>37791.67</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2424-938-CM26</t>
+          <t>4301-480-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11738,17 +11738,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -11777,13 +11777,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>9053.4</v>
+        <v>2923.96</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3515-328-CM26</t>
+          <t>2698-178-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11838,13 +11838,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3453.03</v>
+        <v>7062.75</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4548-437-CM26</t>
+          <t>3515-328-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>9464.540000000001</v>
+        <v>3453.03</v>
       </c>
     </row>
     <row r="181">
@@ -11970,7 +11970,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3515-329-CM26</t>
+          <t>2737-451-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11990,17 +11990,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -12025,13 +12025,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3581.02</v>
+        <v>16564.59</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2737-451-CM26</t>
+          <t>3515-329-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12051,17 +12051,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -12086,13 +12086,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>16564.59</v>
+        <v>3581.02</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2698-179-CM26</t>
+          <t>4105-481-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.051.200-9</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12132,28 +12132,32 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1115.07</v>
+        <v>4637.43</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1134432-525-CM26</t>
+          <t>3776-377-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12178,12 +12182,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12193,28 +12197,32 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>650.48</v>
+        <v>25782.06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4301-489-CM26</t>
+          <t>1134432-525-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12234,17 +12242,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12254,32 +12262,28 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1649.2</v>
+        <v>650.48</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4105-481-CM26</t>
+          <t>2698-179-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12304,12 +12308,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.051.200-9</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALLE LARGA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12319,32 +12323,28 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.209.677-3</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>4637.43</v>
+        <v>1115.07</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3776-376-CM26</t>
+          <t>4301-489-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12364,17 +12364,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12384,28 +12384,32 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6122.19</v>
+        <v>1649.2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3776-377-CM26</t>
+          <t>3776-376-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12445,26 +12449,22 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>25782.06</v>
+        <v>6122.19</v>
       </c>
     </row>
     <row r="190">
@@ -13490,7 +13490,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4964-86-CM26</t>
+          <t>3381-193-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>75.245.100-1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>HERALDO CASTRO PALMA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>6.092.291-8</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13545,13 +13545,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1744.93</v>
+        <v>2113.63</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3381-193-CM26</t>
+          <t>4964-86-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>75.245.100-1</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13591,12 +13591,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>HERALDO CASTRO PALMA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>6.092.291-8</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13606,7 +13606,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2113.63</v>
+        <v>1744.93</v>
       </c>
     </row>
     <row r="208">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -14058,6 +14058,384 @@
       </c>
       <c r="M214" s="2" t="n">
         <v>3122.61</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1285502-24-CM26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>69.061.400-6</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>COMERCIAL RENHET SPA</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>828.11</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>4301-669-CM26</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>7580.91</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1285502-25-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>69.061.400-6</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>76.000.258-5</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>4436.89</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2427-952-CM26</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>69.060.900-2</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>323.65</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2755-454-CM26</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>69.073.400-1</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>1795.56</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1285502-27-CM26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>69.061.400-6</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>SOCIEDAD AGRICOLA Y COMERCIAL EL ALMENDRO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>76.000.258-5</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>2458.73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/valparaiso.xlsx
@@ -9828,7 +9828,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
